--- a/hello.xlsx
+++ b/hello.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -9,18 +9,62 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211" fullCalcOnLoad="1"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -48,15 +92,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -98,7 +150,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -133,7 +185,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -341,10 +393,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/hello.xlsx
+++ b/hello.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -28,14 +28,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>나</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -45,6 +37,22 @@
   </si>
   <si>
     <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나 윤수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다 냐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라 마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -394,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -413,7 +421,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -421,10 +429,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -432,10 +440,21 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/hello.xlsx
+++ b/hello.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -28,6 +28,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -37,22 +45,6 @@
   </si>
   <si>
     <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나 윤수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다 냐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>라 마</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>r</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -402,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -421,7 +413,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -429,10 +421,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -440,21 +432,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/hello.xlsx
+++ b/hello.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -9,62 +9,18 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -92,23 +48,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -150,7 +98,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -185,7 +133,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -393,54 +341,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>